--- a/data/공공데이터신규데이터.xlsx
+++ b/data/공공데이터신규데이터.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="7">
   <si>
     <t>년도</t>
   </si>
@@ -22,16 +22,19 @@
     <t>월</t>
   </si>
   <si>
-    <t>회원구분명</t>
+    <t>신청구분명</t>
   </si>
   <si>
     <t>건수</t>
   </si>
   <si>
-    <t>개인</t>
+    <t>부활차</t>
   </si>
   <si>
-    <t>법인및사업자</t>
+    <t>수입차</t>
+  </si>
+  <si>
+    <t>신조차</t>
   </si>
 </sst>
 </file>
@@ -389,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -417,7 +420,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>106740</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -431,7 +434,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>38483</v>
+        <v>13866</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -439,13 +442,13 @@
         <v>2024</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>80791</v>
+        <v>130951</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -456,10 +459,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>32538</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -467,13 +470,13 @@
         <v>2024</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>103861</v>
+        <v>16924</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -481,13 +484,13 @@
         <v>2024</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>41662</v>
+        <v>96072</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -495,13 +498,13 @@
         <v>2024</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
       <c r="D8">
-        <v>97638</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -509,13 +512,13 @@
         <v>2024</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
       </c>
       <c r="D9">
-        <v>46195</v>
+        <v>26220</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -523,13 +526,13 @@
         <v>2024</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>97494</v>
+        <v>118895</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -537,13 +540,13 @@
         <v>2024</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11">
-        <v>44324</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -551,13 +554,13 @@
         <v>2024</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>90701</v>
+        <v>23091</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -565,13 +568,13 @@
         <v>2024</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13">
-        <v>45020</v>
+        <v>120334</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -579,13 +582,13 @@
         <v>2024</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
       </c>
       <c r="D14">
-        <v>98102</v>
+        <v>381</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -593,13 +596,13 @@
         <v>2024</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
       </c>
       <c r="D15">
-        <v>47924</v>
+        <v>27099</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -607,13 +610,13 @@
         <v>2024</v>
       </c>
       <c r="B16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>80460</v>
+        <v>114338</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -621,13 +624,13 @@
         <v>2024</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>38178</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -635,13 +638,13 @@
         <v>2024</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>87901</v>
+        <v>28909</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -649,13 +652,13 @@
         <v>2024</v>
       </c>
       <c r="B19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>42359</v>
+        <v>106472</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -663,13 +666,13 @@
         <v>2024</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
       </c>
       <c r="D20">
-        <v>100993</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -677,13 +680,13 @@
         <v>2024</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
       </c>
       <c r="D21">
-        <v>45332</v>
+        <v>25873</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -691,13 +694,13 @@
         <v>2024</v>
       </c>
       <c r="B22">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>101407</v>
+        <v>119738</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -705,13 +708,13 @@
         <v>2024</v>
       </c>
       <c r="B23">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>44135</v>
+        <v>366</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -719,13 +722,13 @@
         <v>2024</v>
       </c>
       <c r="B24">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>92691</v>
+        <v>26346</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -733,181 +736,181 @@
         <v>2024</v>
       </c>
       <c r="B25">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25">
-        <v>45719</v>
+        <v>91926</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
       </c>
       <c r="D26">
-        <v>86592</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
       </c>
       <c r="D27">
-        <v>37904</v>
+        <v>27594</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>92927</v>
+        <v>102290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>39833</v>
+        <v>410</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>99906</v>
+        <v>24181</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31">
-        <v>46544</v>
+        <v>121734</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
       </c>
       <c r="D32">
-        <v>101456</v>
+        <v>373</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
       </c>
       <c r="D33">
-        <v>52000</v>
+        <v>26901</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D34">
-        <v>98808</v>
+        <v>118268</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>46579</v>
+        <v>434</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B36">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36">
-        <v>98351</v>
+        <v>26807</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>47332</v>
+        <v>111169</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -915,13 +918,13 @@
         <v>2025</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
       </c>
       <c r="D38">
-        <v>99341</v>
+        <v>391</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -929,13 +932,13 @@
         <v>2025</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
       </c>
       <c r="D39">
-        <v>52208</v>
+        <v>17340</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -943,13 +946,13 @@
         <v>2025</v>
       </c>
       <c r="B40">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D40">
-        <v>85709</v>
+        <v>106765</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -957,13 +960,13 @@
         <v>2025</v>
       </c>
       <c r="B41">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D41">
-        <v>42235</v>
+        <v>408</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -971,13 +974,13 @@
         <v>2025</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D42">
-        <v>105680</v>
+        <v>22713</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -985,13 +988,13 @@
         <v>2025</v>
       </c>
       <c r="B43">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D43">
-        <v>51395</v>
+        <v>109639</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -999,13 +1002,13 @@
         <v>2025</v>
       </c>
       <c r="B44">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C44" t="s">
         <v>4</v>
       </c>
       <c r="D44">
-        <v>83389</v>
+        <v>433</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1013,13 +1016,13 @@
         <v>2025</v>
       </c>
       <c r="B45">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
       </c>
       <c r="D45">
-        <v>40908</v>
+        <v>27725</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1027,13 +1030,13 @@
         <v>2025</v>
       </c>
       <c r="B46">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D46">
-        <v>96502</v>
+        <v>118292</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1041,13 +1044,13 @@
         <v>2025</v>
       </c>
       <c r="B47">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D47">
-        <v>48575</v>
+        <v>398</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1055,13 +1058,13 @@
         <v>2025</v>
       </c>
       <c r="B48">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48">
-        <v>96687</v>
+        <v>24275</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1069,69 +1072,433 @@
         <v>2025</v>
       </c>
       <c r="B49">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D49">
-        <v>48920</v>
+        <v>128783</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
       </c>
       <c r="D50">
-        <v>81950</v>
+        <v>356</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
       </c>
       <c r="D51">
-        <v>43034</v>
+        <v>30478</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D52">
-        <v>87479</v>
+        <v>114553</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
+        <v>2025</v>
+      </c>
+      <c r="B53">
+        <v>6</v>
+      </c>
+      <c r="C53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54">
+        <v>2025</v>
+      </c>
+      <c r="B54">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54">
+        <v>29815</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55">
+        <v>2025</v>
+      </c>
+      <c r="B55">
+        <v>6</v>
+      </c>
+      <c r="C55" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55">
+        <v>115535</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56">
+        <v>2025</v>
+      </c>
+      <c r="B56">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57">
+        <v>2025</v>
+      </c>
+      <c r="B57">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57">
+        <v>29082</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58">
+        <v>2025</v>
+      </c>
+      <c r="B58">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58">
+        <v>122115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59">
+        <v>2025</v>
+      </c>
+      <c r="B59">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60">
+        <v>2025</v>
+      </c>
+      <c r="B60">
+        <v>8</v>
+      </c>
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60">
+        <v>29350</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61">
+        <v>2025</v>
+      </c>
+      <c r="B61">
+        <v>8</v>
+      </c>
+      <c r="C61" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61">
+        <v>98242</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62">
+        <v>2025</v>
+      </c>
+      <c r="B62">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63">
+        <v>2025</v>
+      </c>
+      <c r="B63">
+        <v>9</v>
+      </c>
+      <c r="C63" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63">
+        <v>35670</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64">
+        <v>2025</v>
+      </c>
+      <c r="B64">
+        <v>9</v>
+      </c>
+      <c r="C64" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64">
+        <v>121028</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65">
+        <v>2025</v>
+      </c>
+      <c r="B65">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66">
+        <v>2025</v>
+      </c>
+      <c r="B66">
+        <v>10</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66">
+        <v>26242</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67">
+        <v>2025</v>
+      </c>
+      <c r="B67">
+        <v>10</v>
+      </c>
+      <c r="C67" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67">
+        <v>97752</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68">
+        <v>2025</v>
+      </c>
+      <c r="B68">
+        <v>11</v>
+      </c>
+      <c r="C68" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69">
+        <v>2025</v>
+      </c>
+      <c r="B69">
+        <v>11</v>
+      </c>
+      <c r="C69" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69">
+        <v>31692</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70">
+        <v>2025</v>
+      </c>
+      <c r="B70">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70">
+        <v>113041</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71">
+        <v>2025</v>
+      </c>
+      <c r="B71">
+        <v>12</v>
+      </c>
+      <c r="C71" t="s">
+        <v>4</v>
+      </c>
+      <c r="D71">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72">
+        <v>2025</v>
+      </c>
+      <c r="B72">
+        <v>12</v>
+      </c>
+      <c r="C72" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72">
+        <v>30900</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73">
+        <v>2025</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>6</v>
+      </c>
+      <c r="D73">
+        <v>114326</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74">
         <v>2026</v>
       </c>
-      <c r="B53">
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75">
+        <v>2026</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75">
+        <v>23305</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76">
+        <v>2026</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76">
+        <v>101308</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77">
+        <v>2026</v>
+      </c>
+      <c r="B77">
         <v>2</v>
       </c>
-      <c r="C53" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53">
-        <v>40242</v>
+      <c r="C77" t="s">
+        <v>4</v>
+      </c>
+      <c r="D77">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78">
+        <v>2026</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78">
+        <v>28915</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79">
+        <v>2026</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79">
+        <v>98533</v>
       </c>
     </row>
   </sheetData>

--- a/data/공공데이터신규데이터.xlsx
+++ b/data/공공데이터신규데이터.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="7">
   <si>
     <t>년도</t>
   </si>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1501,6 +1501,48 @@
         <v>98533</v>
       </c>
     </row>
+    <row r="80" spans="1:4">
+      <c r="A80">
+        <v>2026</v>
+      </c>
+      <c r="B80">
+        <v>3</v>
+      </c>
+      <c r="C80" t="s">
+        <v>4</v>
+      </c>
+      <c r="D80">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81">
+        <v>2026</v>
+      </c>
+      <c r="B81">
+        <v>3</v>
+      </c>
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81">
+        <v>36479</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82">
+        <v>2026</v>
+      </c>
+      <c r="B82">
+        <v>3</v>
+      </c>
+      <c r="C82" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82">
+        <v>126200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/공공데이터신규데이터.xlsx
+++ b/data/공공데이터신규데이터.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="7">
   <si>
     <t>년도</t>
   </si>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1543,6 +1543,48 @@
         <v>126200</v>
       </c>
     </row>
+    <row r="83" spans="1:4">
+      <c r="A83">
+        <v>2026</v>
+      </c>
+      <c r="B83">
+        <v>4</v>
+      </c>
+      <c r="C83" t="s">
+        <v>4</v>
+      </c>
+      <c r="D83">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84">
+        <v>2026</v>
+      </c>
+      <c r="B84">
+        <v>4</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84">
+        <v>36470</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85">
+        <v>2026</v>
+      </c>
+      <c r="B85">
+        <v>4</v>
+      </c>
+      <c r="C85" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85">
+        <v>121341</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/공공데이터신규데이터.xlsx
+++ b/data/공공데이터신규데이터.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="7">
   <si>
     <t>년도</t>
   </si>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1585,6 +1585,48 @@
         <v>121341</v>
       </c>
     </row>
+    <row r="86" spans="1:4">
+      <c r="A86">
+        <v>2026</v>
+      </c>
+      <c r="B86">
+        <v>5</v>
+      </c>
+      <c r="C86" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87">
+        <v>2026</v>
+      </c>
+      <c r="B87">
+        <v>5</v>
+      </c>
+      <c r="C87" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87">
+        <v>32131</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88">
+        <v>2026</v>
+      </c>
+      <c r="B88">
+        <v>5</v>
+      </c>
+      <c r="C88" t="s">
+        <v>6</v>
+      </c>
+      <c r="D88">
+        <v>90634</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/공공데이터신규데이터.xlsx
+++ b/data/공공데이터신규데이터.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="7">
   <si>
     <t>년도</t>
   </si>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1627,6 +1627,48 @@
         <v>90634</v>
       </c>
     </row>
+    <row r="89" spans="1:4">
+      <c r="A89">
+        <v>2026</v>
+      </c>
+      <c r="B89">
+        <v>6</v>
+      </c>
+      <c r="C89" t="s">
+        <v>4</v>
+      </c>
+      <c r="D89">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90">
+        <v>2026</v>
+      </c>
+      <c r="B90">
+        <v>6</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90">
+        <v>40066</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91">
+        <v>2026</v>
+      </c>
+      <c r="B91">
+        <v>6</v>
+      </c>
+      <c r="C91" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91">
+        <v>122022</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
